--- a/Flag/Extrair DP/planilhas/Linhas de Cuidado - Cardio Arritmia (1).xlsx
+++ b/Flag/Extrair DP/planilhas/Linhas de Cuidado - Cardio Arritmia (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30203"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30210"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmdpcombr-my.sharepoint.com/personal/anderson_cmdp_com_br/Documents/987 - IPIRANGA/ENFERMAGEM CMDP IPIRANGA/CMDP - LINHAS DE CUIDADO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="563" documentId="8_{934DE081-6835-42C8-A318-5D83D1296085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29092AE1-80F1-48A4-9651-90BBDD0E8EF2}"/>
+  <xr:revisionPtr revIDLastSave="573" documentId="8_{934DE081-6835-42C8-A318-5D83D1296085}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F38858EA-665A-4ECD-AF04-53EA197783B1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="781" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="781" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Consolidado" sheetId="32" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3601" uniqueCount="669">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3612" uniqueCount="672">
   <si>
     <t xml:space="preserve">Prioridade no Contato? </t>
   </si>
@@ -1477,6 +1477,15 @@
   </si>
   <si>
     <t>21-990143863</t>
+  </si>
+  <si>
+    <t>THAIS REGINA KOSHIYAMA</t>
+  </si>
+  <si>
+    <t>VILA ARRIETE</t>
+  </si>
+  <si>
+    <t>11996334228 11996334228</t>
   </si>
   <si>
     <t>Situação Atual do Paciente</t>
@@ -4367,10 +4376,10 @@
   <cols>
     <col min="1" max="1" width="11" style="31" customWidth="1"/>
     <col min="2" max="2" width="11.5703125" style="27" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" style="29" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" style="29" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" style="29" customWidth="1"/>
     <col min="5" max="5" width="11.7109375" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="31.85546875" style="223" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.28515625" style="223" customWidth="1"/>
     <col min="7" max="7" width="12" style="30" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.140625" style="27" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.28515625" style="30" bestFit="1" customWidth="1"/>
@@ -22136,21 +22145,49 @@
       </c>
     </row>
     <row r="133" spans="1:47" ht="12" customHeight="1">
-      <c r="A133" s="87"/>
-      <c r="B133" s="93"/>
-      <c r="C133" s="89"/>
-      <c r="D133" s="89"/>
-      <c r="E133" s="112"/>
-      <c r="F133" s="221"/>
-      <c r="G133" s="113"/>
-      <c r="H133" s="98"/>
+      <c r="A133" s="87" t="s">
+        <v>66</v>
+      </c>
+      <c r="B133" s="93">
+        <v>46188</v>
+      </c>
+      <c r="C133" s="89" t="s">
+        <v>440</v>
+      </c>
+      <c r="D133" s="89" t="s">
+        <v>49</v>
+      </c>
+      <c r="E133" s="112">
+        <v>94048807</v>
+      </c>
+      <c r="F133" s="221" t="s">
+        <v>470</v>
+      </c>
+      <c r="G133" s="113">
+        <v>25077361860</v>
+      </c>
+      <c r="H133" s="98">
+        <v>27199</v>
+      </c>
       <c r="I133" s="92"/>
-      <c r="J133" s="114"/>
-      <c r="K133" s="89"/>
-      <c r="L133" s="89"/>
-      <c r="M133" s="89"/>
-      <c r="N133" s="89"/>
-      <c r="O133" s="91"/>
+      <c r="J133" s="114" t="s">
+        <v>391</v>
+      </c>
+      <c r="K133" s="89" t="s">
+        <v>51</v>
+      </c>
+      <c r="L133" s="89" t="s">
+        <v>52</v>
+      </c>
+      <c r="M133" s="89" t="s">
+        <v>471</v>
+      </c>
+      <c r="N133" s="89">
+        <v>110</v>
+      </c>
+      <c r="O133" s="91" t="s">
+        <v>472</v>
+      </c>
       <c r="P133" s="95"/>
       <c r="Q133" s="145"/>
       <c r="R133" s="122"/>
@@ -22171,18 +22208,22 @@
       <c r="AG133" s="119"/>
       <c r="AH133" s="119"/>
       <c r="AI133" s="100"/>
-      <c r="AJ133" s="100"/>
-      <c r="AK133" s="100"/>
+      <c r="AJ133" s="100" t="s">
+        <v>66</v>
+      </c>
+      <c r="AK133" s="100" t="s">
+        <v>66</v>
+      </c>
       <c r="AL133" s="45" t="s">
         <v>67</v>
       </c>
       <c r="AM133" s="199" t="str">
         <f t="shared" si="24"/>
-        <v>1/1900</v>
-      </c>
-      <c r="AN133" s="45" t="e">
+        <v>6/2026</v>
+      </c>
+      <c r="AN133" s="45">
         <f t="shared" si="25"/>
-        <v>#NUM!</v>
+        <v>3</v>
       </c>
       <c r="AO133" s="45" t="str">
         <f t="shared" si="26"/>
@@ -26963,7 +27004,7 @@
         <v>0</v>
       </c>
       <c r="AT194" s="45">
-        <f t="shared" ref="AT194:AT257" si="43">IF(AU194="S",IF(AND(Q194="1. Aceitou o programa",AB194="Realizada"),IFERROR(IF(AA194="",0,AA194-R194),0),0),0)</f>
+        <f t="shared" ref="AT194:AT240" si="43">IF(AU194="S",IF(AND(Q194="1. Aceitou o programa",AB194="Realizada"),IFERROR(IF(AA194="",0,AA194-R194),0),0),0)</f>
         <v>0</v>
       </c>
       <c r="AU194" s="45" t="str">
@@ -62787,10 +62828,10 @@
     </row>
     <row r="4" spans="1:31">
       <c r="B4" s="211" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C4" s="81" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="F4" s="40"/>
     </row>
@@ -62808,12 +62849,12 @@
         <v>46143</v>
       </c>
       <c r="D7" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:31">
       <c r="B9" s="213" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="C9" s="78">
         <v>46023</v>
@@ -62821,7 +62862,7 @@
     </row>
     <row r="10" spans="1:31">
       <c r="B10" s="213" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="C10" s="78">
         <v>46181</v>
@@ -62830,7 +62871,7 @@
     <row r="12" spans="1:31" s="219" customFormat="1">
       <c r="A12" s="217"/>
       <c r="B12" s="218" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C12" s="217"/>
       <c r="D12" s="217"/>
@@ -62874,11 +62915,11 @@
       <c r="F14" s="176"/>
       <c r="G14" s="176"/>
       <c r="H14" s="176" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="I14" s="176"/>
       <c r="K14" s="237" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="L14" s="176" t="s">
         <v>39</v>
@@ -62892,13 +62933,13 @@
         <v>16</v>
       </c>
       <c r="T14" s="77" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="U14" s="77" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="W14" s="186" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="X14" s="186"/>
       <c r="Y14" s="186"/>
@@ -62921,10 +62962,10 @@
         <v>5</v>
       </c>
       <c r="H15" s="176" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="I15" s="176" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="K15" s="237"/>
       <c r="L15" s="177">
@@ -62943,7 +62984,7 @@
         <v>5</v>
       </c>
       <c r="Q15" s="176" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="S15" s="193" t="s">
         <v>56</v>
@@ -62957,7 +62998,7 @@
         <v>0.88372093023255816</v>
       </c>
       <c r="W15" s="187" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="X15" s="187"/>
       <c r="Y15" s="188">
@@ -62998,7 +63039,7 @@
         <v>0.88617886178861793</v>
       </c>
       <c r="K16" s="36" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="L16" s="36">
         <f t="shared" ref="L16:Q16" si="2">+C41</f>
@@ -63025,7 +63066,7 @@
         <v>123</v>
       </c>
       <c r="S16" s="206" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="T16" s="38">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S16,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63036,7 +63077,7 @@
         <v>0</v>
       </c>
       <c r="W16" s="208" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="X16" s="208"/>
       <c r="Y16" s="210">
@@ -63046,7 +63087,7 @@
     </row>
     <row r="17" spans="2:25">
       <c r="B17" s="195" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C17" s="38">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B17,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63104,7 +63145,7 @@
         <v>109</v>
       </c>
       <c r="S17" s="193" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="T17" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S17,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63115,7 +63156,7 @@
         <v>0</v>
       </c>
       <c r="W17" s="187" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="X17" s="187"/>
       <c r="Y17" s="189">
@@ -63125,7 +63166,7 @@
     </row>
     <row r="18" spans="2:25">
       <c r="B18" s="194" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C18" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B18,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63156,7 +63197,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="194" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="L18" s="41" t="str">
         <f t="shared" ref="L18:Q18" si="5">IFERROR(L17/L16,"")</f>
@@ -63183,7 +63224,7 @@
         <v>0.88617886178861793</v>
       </c>
       <c r="S18" s="206" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="T18" s="38">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S18,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63194,7 +63235,7 @@
         <v>0</v>
       </c>
       <c r="W18" s="208" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="X18" s="208"/>
       <c r="Y18" s="210">
@@ -63204,7 +63245,7 @@
     </row>
     <row r="19" spans="2:25">
       <c r="B19" s="195" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C19" s="38">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B19,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63235,7 +63276,7 @@
         <v>0</v>
       </c>
       <c r="K19" s="195" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="L19" s="178">
         <f>IFERROR(SUMIFS(Consolidado!$AQ:$AQ,Consolidado!$AN:$AN,Análise!L15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3))/L$17,0)</f>
@@ -63262,7 +63303,7 @@
         <v>6.9357798165137616</v>
       </c>
       <c r="S19" s="193" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="T19" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S19,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63273,7 +63314,7 @@
         <v>0</v>
       </c>
       <c r="W19" s="187" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="X19" s="187"/>
       <c r="Y19" s="189">
@@ -63283,7 +63324,7 @@
     </row>
     <row r="20" spans="2:25">
       <c r="B20" s="194" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C20" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B20,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63314,7 +63355,7 @@
         <v>0</v>
       </c>
       <c r="K20" s="194" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="L20" s="179">
         <f>IFERROR(SUMIFS(Consolidado!$AS:$AS,Consolidado!$AN:$AN,Análise!L15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3))/COUNTIFS(Consolidado!$AN:$AN,Análise!L15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,$K17,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AS:$AS,"&lt;&gt;"&amp;0),0)</f>
@@ -63341,7 +63382,7 @@
         <v>7.75</v>
       </c>
       <c r="S20" s="206" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="T20" s="38">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S20,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63352,7 +63393,7 @@
         <v>0</v>
       </c>
       <c r="W20" s="208" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="X20" s="208"/>
       <c r="Y20" s="209">
@@ -63362,7 +63403,7 @@
     </row>
     <row r="21" spans="2:25">
       <c r="B21" s="195" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C21" s="38">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B21,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63393,7 +63434,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="195" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="L21" s="178">
         <f>IFERROR(SUMIFS(Consolidado!$AT:$AT,Consolidado!$AN:$AN,Análise!L15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3))/COUNTIFS(Consolidado!$AN:$AN,Análise!L15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,$K17,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AT:$AT,"&lt;&gt;"&amp;0),0)</f>
@@ -63420,7 +63461,7 @@
         <v>13.450441919191773</v>
       </c>
       <c r="S21" s="193" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="T21" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S21,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63433,7 +63474,7 @@
     </row>
     <row r="22" spans="2:25">
       <c r="B22" s="194" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C22" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B22,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63464,7 +63505,7 @@
         <v>0</v>
       </c>
       <c r="S22" s="206" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="T22" s="38">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S22,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63475,18 +63516,18 @@
         <v>0</v>
       </c>
       <c r="W22" s="77" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="X22" s="77" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="Y22" s="77" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="23" spans="2:25">
       <c r="B23" s="195" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C23" s="38">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B23,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63517,7 +63558,7 @@
         <v>0</v>
       </c>
       <c r="S23" s="193" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="T23" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S23,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63541,7 +63582,7 @@
     </row>
     <row r="24" spans="2:25">
       <c r="B24" s="194" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="C24" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B24,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63572,7 +63613,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="237" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="L24" s="176" t="s">
         <v>39</v>
@@ -63583,7 +63624,7 @@
       <c r="P24" s="176"/>
       <c r="Q24" s="176"/>
       <c r="S24" s="206" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="T24" s="38">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S24,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63607,7 +63648,7 @@
     </row>
     <row r="25" spans="2:25">
       <c r="B25" s="195" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C25" s="38">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B25,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63654,10 +63695,10 @@
         <v>5</v>
       </c>
       <c r="Q25" s="176" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="S25" s="193" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="T25" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S25,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63670,7 +63711,7 @@
     </row>
     <row r="26" spans="2:25">
       <c r="B26" s="194" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="C26" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B26,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63701,7 +63742,7 @@
         <v>0</v>
       </c>
       <c r="K26" s="36" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="L26" s="75">
         <f>IFERROR(SUMIFS(Consolidado!AR:AR,Consolidado!$AN:$AN,L25,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3))/COUNTIFS(Consolidado!$R:$R,"&lt;&gt;",Consolidado!$S:$S,"&lt;&gt;",Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AN:$AN,L25),0)</f>
@@ -63728,7 +63769,7 @@
         <v>14.5</v>
       </c>
       <c r="S26" s="206" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="T26" s="38">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S26,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63741,7 +63782,7 @@
     </row>
     <row r="27" spans="2:25">
       <c r="B27" s="195" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="C27" s="38">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B27,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63772,7 +63813,7 @@
         <v>0</v>
       </c>
       <c r="S27" s="193" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="T27" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S27,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63785,7 +63826,7 @@
     </row>
     <row r="28" spans="2:25">
       <c r="B28" s="194" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C28" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B28,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63860,7 +63901,7 @@
         <v>3.2520325203252036E-2</v>
       </c>
       <c r="K29" s="237" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="L29" s="176" t="s">
         <v>39</v>
@@ -63871,7 +63912,7 @@
       <c r="P29" s="176"/>
       <c r="Q29" s="176"/>
       <c r="S29" s="193" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="T29" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S29,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63884,7 +63925,7 @@
     </row>
     <row r="30" spans="2:25">
       <c r="B30" s="194" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C30" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B30,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63931,10 +63972,10 @@
         <v>5</v>
       </c>
       <c r="Q30" s="176" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="S30" s="206" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="T30" s="38">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S30,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63947,7 +63988,7 @@
     </row>
     <row r="31" spans="2:25">
       <c r="B31" s="195" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="C31" s="38">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B31,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -63978,7 +64019,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="38" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="L31" s="183" t="str">
         <f t="shared" ref="L31:Q31" si="6">IFERROR((C16+C38)/C41,"")</f>
@@ -64049,7 +64090,7 @@
         <v>3.2520325203252036E-2</v>
       </c>
       <c r="S32" s="206" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="T32" s="38">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S32,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64062,7 +64103,7 @@
     </row>
     <row r="33" spans="1:31">
       <c r="B33" s="195" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C33" s="38">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B33,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64093,7 +64134,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="193" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="T33" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S33,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64106,7 +64147,7 @@
     </row>
     <row r="34" spans="1:31">
       <c r="B34" s="194" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C34" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B34,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64137,16 +64178,16 @@
         <v>0</v>
       </c>
       <c r="K34" s="37" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="L34" s="37" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="M34" s="176" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="S34" s="206" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="T34" s="38">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S34,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64159,7 +64200,7 @@
     </row>
     <row r="35" spans="1:31">
       <c r="B35" s="195" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="C35" s="38">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B35,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64201,7 +64242,7 @@
         <v>0.375</v>
       </c>
       <c r="S35" s="193" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="T35" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S35,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64214,7 +64255,7 @@
     </row>
     <row r="36" spans="1:31">
       <c r="B36" s="194" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="C36" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B36,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64256,7 +64297,7 @@
         <v>0.625</v>
       </c>
       <c r="S36" s="206" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="T36" s="38">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S36,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64269,7 +64310,7 @@
     </row>
     <row r="37" spans="1:31">
       <c r="B37" s="195" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C37" s="38">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B37,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64344,7 +64385,7 @@
         <v>4.878048780487805E-2</v>
       </c>
       <c r="S38" s="206" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="T38" s="38">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S38,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64357,7 +64398,7 @@
     </row>
     <row r="39" spans="1:31">
       <c r="B39" s="195" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="C39" s="38">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B39,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64388,7 +64429,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="193" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="T39" s="79">
         <f>COUNTIFS(Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!S39,Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64401,7 +64442,7 @@
     </row>
     <row r="40" spans="1:31">
       <c r="B40" s="194" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C40" s="36">
         <f>COUNTIFS(Consolidado!$AN:$AN,Análise!C$15,Consolidado!$AM:$AM,Análise!$C$7,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$Q:$Q,Análise!$B40,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -64432,7 +64473,7 @@
         <v>0</v>
       </c>
       <c r="S40" s="207" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="T40" s="39">
         <f>SUM(T15:T39)</f>
@@ -64445,7 +64486,7 @@
     </row>
     <row r="41" spans="1:31">
       <c r="B41" s="39" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C41" s="39">
         <f t="shared" ref="C41:H41" si="7">SUM(C16:C40)</f>
@@ -64479,7 +64520,7 @@
     <row r="43" spans="1:31" s="219" customFormat="1">
       <c r="A43" s="217"/>
       <c r="B43" s="218" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C43" s="217"/>
       <c r="D43" s="217"/>
@@ -64523,7 +64564,7 @@
       <c r="F45" s="176"/>
       <c r="G45" s="176"/>
       <c r="H45" s="238" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="46" spans="1:31">
@@ -64579,7 +64620,7 @@
         <v>16</v>
       </c>
       <c r="C49" s="77" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="50" spans="1:31">
@@ -64594,7 +64635,7 @@
     <row r="52" spans="1:31" s="219" customFormat="1">
       <c r="A52" s="217"/>
       <c r="B52" s="218" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="C52" s="217"/>
       <c r="D52" s="217"/>
@@ -64628,7 +64669,7 @@
     </row>
     <row r="54" spans="1:31">
       <c r="B54" s="233" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="C54" s="176" t="s">
         <v>39</v>
@@ -64639,10 +64680,10 @@
       <c r="G54" s="176"/>
       <c r="H54" s="176"/>
       <c r="K54" s="234" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="L54" s="235" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="55" spans="1:31">
@@ -64663,14 +64704,14 @@
         <v>5</v>
       </c>
       <c r="H55" s="37" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="K55" s="234"/>
       <c r="L55" s="236"/>
     </row>
     <row r="56" spans="1:31">
       <c r="B56" s="47" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C56" s="36">
         <f>COUNTIFS(Consolidado!$AF:$AF,$B56,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,Análise!C$55,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AU:$AU,"S")</f>
@@ -64697,7 +64738,7 @@
         <v>0</v>
       </c>
       <c r="K56" s="204" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="L56" s="79">
         <f>COUNTIFS(Consolidado!$AF:$AF,$K56,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AU:$AU,"S")</f>
@@ -64706,7 +64747,7 @@
     </row>
     <row r="57" spans="1:31">
       <c r="B57" s="48" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C57" s="38">
         <f>COUNTIFS(Consolidado!$AF:$AF,$B57,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,Análise!C$55,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AU:$AU,"S")</f>
@@ -64733,7 +64774,7 @@
         <v>0</v>
       </c>
       <c r="K57" s="48" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="L57" s="38">
         <f>COUNTIFS(Consolidado!$AF:$AF,$K57,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AU:$AU,"S")</f>
@@ -64742,7 +64783,7 @@
     </row>
     <row r="58" spans="1:31">
       <c r="B58" s="47" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C58" s="36">
         <f>COUNTIFS(Consolidado!$AF:$AF,$B58,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,Análise!C$55,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AU:$AU,"S")</f>
@@ -64769,7 +64810,7 @@
         <v>0</v>
       </c>
       <c r="K58" s="204" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="L58" s="79">
         <f>COUNTIFS(Consolidado!$AF:$AF,$K58,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AU:$AU,"S")</f>
@@ -64886,7 +64927,7 @@
     </row>
     <row r="62" spans="1:31">
       <c r="B62" s="47" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C62" s="44">
         <f>SUM(C56:C61)</f>
@@ -64913,7 +64954,7 @@
         <v>9</v>
       </c>
       <c r="K62" s="204" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="L62" s="205">
         <f>SUM(L56:L61)</f>
@@ -64922,7 +64963,7 @@
     </row>
     <row r="64" spans="1:31">
       <c r="B64" s="233" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="C64" s="176" t="s">
         <v>39</v>
@@ -64933,10 +64974,10 @@
       <c r="G64" s="176"/>
       <c r="H64" s="176"/>
       <c r="K64" s="234" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="L64" s="235" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="65" spans="1:31">
@@ -64957,14 +64998,14 @@
         <v>5</v>
       </c>
       <c r="H65" s="37" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="K65" s="234"/>
       <c r="L65" s="236"/>
     </row>
     <row r="66" spans="1:31">
       <c r="B66" s="47" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="C66" s="41" t="str">
         <f>IFERROR(COUNTIFS(Consolidado!$AG:$AG,$B66,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,Análise!C$65,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AF:$AF,"&lt;&gt;",Consolidado!$AF:$AF,"&lt;&gt;"&amp;$B66,Consolidado!$AU:$AU,"S")/(C$59+C$60+C$61),"")</f>
@@ -64991,7 +65032,7 @@
         <v>0</v>
       </c>
       <c r="K66" s="204" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="L66" s="80">
         <f>IFERROR(COUNTIFS(Consolidado!$AG:$AG,$K66,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AF:$AF,"&lt;&gt;",Consolidado!$AF:$AF,"&lt;&gt;"&amp;$K66,Consolidado!$AU:$AU,"S")/(L$59+L$60+L$61),"")</f>
@@ -65000,7 +65041,7 @@
     </row>
     <row r="67" spans="1:31">
       <c r="B67" s="48" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="C67" s="42" t="str">
         <f>IFERROR(COUNTIFS(Consolidado!$AG:$AG,$B67,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,Análise!C$65,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AF:$AF,"&lt;&gt;",Consolidado!$AF:$AF,"&lt;&gt;"&amp;$B67,Consolidado!$AU:$AU,"S")/(C$59+C$60+C$61),"")</f>
@@ -65027,7 +65068,7 @@
         <v>0</v>
       </c>
       <c r="K67" s="48" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="L67" s="42">
         <f>IFERROR(COUNTIFS(Consolidado!$AG:$AG,$K67,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AF:$AF,"&lt;&gt;",Consolidado!$AF:$AF,"&lt;&gt;"&amp;$K67,Consolidado!$AU:$AU,"S")/(L$59+L$60+L$61),"")</f>
@@ -65036,7 +65077,7 @@
     </row>
     <row r="68" spans="1:31">
       <c r="B68" s="47" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="C68" s="41" t="str">
         <f>IFERROR(COUNTIFS(Consolidado!$AG:$AG,$B68,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,Análise!C$65,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AF:$AF,"&lt;&gt;",Consolidado!$AF:$AF,"&lt;&gt;"&amp;$B68,Consolidado!$AU:$AU,"S")/(C$59+C$60+C$61),"")</f>
@@ -65063,7 +65104,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="204" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="L68" s="80">
         <f>IFERROR(COUNTIFS(Consolidado!$AG:$AG,$K68,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AF:$AF,"&lt;&gt;",Consolidado!$AF:$AF,"&lt;&gt;"&amp;$K68,Consolidado!$AU:$AU,"S")/(L$59+L$60+L$61),"")</f>
@@ -65073,7 +65114,7 @@
     <row r="70" spans="1:31" s="219" customFormat="1">
       <c r="A70" s="217"/>
       <c r="B70" s="218" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="C70" s="217"/>
       <c r="D70" s="217"/>
@@ -65107,7 +65148,7 @@
     </row>
     <row r="72" spans="1:31">
       <c r="B72" s="35" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C72" s="46">
         <v>1</v>
@@ -65125,13 +65166,13 @@
         <v>5</v>
       </c>
       <c r="H72" s="46" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="K72" s="76" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="L72" s="214" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="73" spans="1:31">
@@ -65208,7 +65249,7 @@
     </row>
     <row r="75" spans="1:31">
       <c r="B75" s="47" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C75" s="36">
         <f>COUNTIFS(Consolidado!$AH:$AH,$B75,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,Análise!C$55,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AU:$AU,"S")</f>
@@ -65235,7 +65276,7 @@
         <v>0</v>
       </c>
       <c r="K75" s="204" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="L75" s="79">
         <f>COUNTIFS(Consolidado!$AH:$AH,$B75,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Q:$Q,"1. Aceitou o programa",Consolidado!$AU:$AU,"S")</f>
@@ -65244,7 +65285,7 @@
     </row>
     <row r="76" spans="1:31">
       <c r="B76" s="48" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C76" s="39">
         <f>SUM(C73:C75)</f>
@@ -65271,7 +65312,7 @@
         <v>43</v>
       </c>
       <c r="K76" s="48" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="L76" s="39">
         <f>SUM(L73:L75)</f>
@@ -65280,16 +65321,16 @@
     </row>
     <row r="78" spans="1:31">
       <c r="B78" s="35" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C78" s="46" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="K78" s="76" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="L78" s="214" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="79" spans="1:31">
@@ -65326,14 +65367,14 @@
     </row>
     <row r="81" spans="1:31">
       <c r="B81" s="47" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="C81" s="51">
         <f>IFERROR(H75/$H$76,"")</f>
         <v>0</v>
       </c>
       <c r="K81" s="204" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="L81" s="216">
         <f>IFERROR(L75/$L$76,"")</f>
@@ -65343,7 +65384,7 @@
     <row r="83" spans="1:31" s="219" customFormat="1">
       <c r="A83" s="217"/>
       <c r="B83" s="218" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="C83" s="217"/>
       <c r="D83" s="217"/>
@@ -65377,7 +65418,7 @@
     </row>
     <row r="85" spans="1:31">
       <c r="B85" s="35" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="C85" s="46">
         <v>1</v>
@@ -65395,13 +65436,13 @@
         <v>5</v>
       </c>
       <c r="H85" s="46" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="K85" s="76" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="L85" s="214" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="86" spans="1:31">
@@ -65442,7 +65483,7 @@
     </row>
     <row r="87" spans="1:31">
       <c r="B87" s="48" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="C87" s="38">
         <f>COUNTIFS(Consolidado!$Z:$Z,$B87,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,Análise!C$55,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65469,7 +65510,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="48" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="L87" s="38">
         <f>COUNTIFS(Consolidado!$Z:$Z,$B87,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65514,7 +65555,7 @@
     </row>
     <row r="89" spans="1:31">
       <c r="B89" s="48" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C89" s="39">
         <f>SUM(C86:C88)</f>
@@ -65541,7 +65582,7 @@
         <v>117</v>
       </c>
       <c r="K89" s="48" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="L89" s="39">
         <f>SUM(L86:L88)</f>
@@ -65550,7 +65591,7 @@
     </row>
     <row r="91" spans="1:31">
       <c r="B91" s="35" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C91" s="46">
         <v>1</v>
@@ -65568,13 +65609,13 @@
         <v>5</v>
       </c>
       <c r="H91" s="46" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="K91" s="76" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="L91" s="214" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="92" spans="1:31">
@@ -65615,7 +65656,7 @@
     </row>
     <row r="93" spans="1:31">
       <c r="B93" s="48" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C93" s="38">
         <f>COUNTIFS(Consolidado!$AB:$AB,$B93,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,C$91,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Z:$Z,"Agendada",Consolidado!$AU:$AU,"S")</f>
@@ -65642,7 +65683,7 @@
         <v>0</v>
       </c>
       <c r="K93" s="48" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="L93" s="38">
         <f>COUNTIFS(Consolidado!$AB:$AB,$B93,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Z:$Z,"Agendada",Consolidado!$AU:$AU,"S")</f>
@@ -65759,7 +65800,7 @@
     </row>
     <row r="97" spans="1:31">
       <c r="B97" s="48" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="C97" s="38">
         <f>COUNTIFS(Consolidado!$AB:$AB,$B97,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,C$91,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Z:$Z,"Agendada",Consolidado!$AU:$AU,"S")</f>
@@ -65786,7 +65827,7 @@
         <v>0</v>
       </c>
       <c r="K97" s="48" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="L97" s="38">
         <f>COUNTIFS(Consolidado!$AB:$AB,$B97,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$Z:$Z,"Agendada",Consolidado!$AU:$AU,"S")</f>
@@ -65795,7 +65836,7 @@
     </row>
     <row r="98" spans="1:31">
       <c r="B98" s="47" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C98" s="44">
         <f t="shared" ref="C98:H98" si="14">SUM(C92:C97)</f>
@@ -65822,7 +65863,7 @@
         <v>113</v>
       </c>
       <c r="K98" s="204" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="L98" s="205">
         <f>SUM(L92:L97)</f>
@@ -65832,7 +65873,7 @@
     <row r="100" spans="1:31" s="219" customFormat="1">
       <c r="A100" s="217"/>
       <c r="B100" s="218" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="C100" s="217"/>
       <c r="D100" s="217"/>
@@ -65884,7 +65925,7 @@
         <v>3</v>
       </c>
       <c r="L102" s="235" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="103" spans="1:31">
@@ -65905,7 +65946,7 @@
         <v>5</v>
       </c>
       <c r="H103" s="37" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="K103" s="234"/>
       <c r="L103" s="236"/>
@@ -65948,7 +65989,7 @@
     </row>
     <row r="105" spans="1:31">
       <c r="B105" s="48" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="C105" s="38">
         <f>COUNTIFS(Consolidado!$D:$D,$B105,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,C$103,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -65975,7 +66016,7 @@
         <v>0</v>
       </c>
       <c r="K105" s="48" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="L105" s="38">
         <f>COUNTIFS(Consolidado!$D:$D,$K105,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -66020,7 +66061,7 @@
     </row>
     <row r="107" spans="1:31">
       <c r="B107" s="48" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C107" s="38">
         <f>COUNTIFS(Consolidado!$D:$D,$B107,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,C$103,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -66047,7 +66088,7 @@
         <v>0</v>
       </c>
       <c r="K107" s="48" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="L107" s="38">
         <f>COUNTIFS(Consolidado!$D:$D,$K107,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -66056,7 +66097,7 @@
     </row>
     <row r="108" spans="1:31">
       <c r="B108" s="47" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="C108" s="36">
         <f>COUNTIFS(Consolidado!$D:$D,$B108,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,C$103,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -66083,7 +66124,7 @@
         <v>0</v>
       </c>
       <c r="K108" s="204" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="L108" s="79">
         <f>COUNTIFS(Consolidado!$D:$D,$K108,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -66092,7 +66133,7 @@
     </row>
     <row r="109" spans="1:31">
       <c r="B109" s="48" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C109" s="38">
         <f>COUNTIFS(Consolidado!$D:$D,$B109,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,C$103,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -66119,7 +66160,7 @@
         <v>0</v>
       </c>
       <c r="K109" s="48" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="L109" s="38">
         <f>COUNTIFS(Consolidado!$D:$D,$K109,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -66128,7 +66169,7 @@
     </row>
     <row r="110" spans="1:31">
       <c r="B110" s="47" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C110" s="36">
         <f>COUNTIFS(Consolidado!$D:$D,$B110,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$AM:$AM,$C$7,Consolidado!$AN:$AN,C$103,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -66155,7 +66196,7 @@
         <v>0</v>
       </c>
       <c r="K110" s="204" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="L110" s="79">
         <f>COUNTIFS(Consolidado!$D:$D,$K110,Consolidado!$AL:$AL,IF(ISBLANK($C$2),"&lt;&gt;",$C$2),Consolidado!$B:$B,"&lt;="&amp;Análise!$C$10,Consolidado!$B:$B,"&gt;="&amp;Análise!$C$9,Consolidado!$C:$C,IF(ISBLANK($C$3),"&lt;&gt;",$C$3),Consolidado!$AU:$AU,"S")</f>
@@ -66164,7 +66205,7 @@
     </row>
     <row r="111" spans="1:31">
       <c r="B111" s="48" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C111" s="39">
         <f>SUM(C104:C110)</f>
@@ -66191,7 +66232,7 @@
         <v>123</v>
       </c>
       <c r="K111" s="48" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="L111" s="39">
         <f>SUM(L104:L110)</f>
@@ -66299,33 +66340,33 @@
         <v>2</v>
       </c>
       <c r="F1" s="67" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="G1" s="53"/>
       <c r="H1" s="155" t="s">
         <v>37</v>
       </c>
       <c r="I1" s="154" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="K1" s="71" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="L1" s="53"/>
       <c r="M1" s="54" t="s">
         <v>37</v>
       </c>
       <c r="N1" s="55" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="P1" s="158" t="s">
         <v>32</v>
       </c>
       <c r="R1" s="56" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="T1" s="74" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="V1" s="170" t="s">
         <v>16</v>
@@ -66346,7 +66387,7 @@
         <v>29</v>
       </c>
       <c r="AH1" s="161" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="AJ1" s="162" t="s">
         <v>35</v>
@@ -66360,17 +66401,17 @@
     </row>
     <row r="2" spans="2:40" ht="15" thickBot="1">
       <c r="B2" s="52" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="D2" s="148" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F2" s="70" t="str" cm="1">
         <f t="array" ref="F2:F10">IF(COUNTIF(Consolidado!$AL:$AL,"Emagrecimento")&lt;&gt;0,_xlfn._xlws.FILTER($I$2:$I$54,$H$2:$H$54&lt;&gt;""),_xlfn._xlws.FILTER($I$2:$I$54,$H$2:$H$54="Outras"))</f>
         <v>Captado pela Amil/Call Center</v>
       </c>
       <c r="H2" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="I2" s="150" t="s">
         <v>49</v>
@@ -66380,16 +66421,16 @@
         <v>Amil Paulistano</v>
       </c>
       <c r="M2" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N2" s="151" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="P2" s="159" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="R2" s="59" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="T2" s="85" t="s">
         <v>83</v>
@@ -66433,31 +66474,31 @@
         <v>Casos Prioritário - E-mail</v>
       </c>
       <c r="H3" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="I3" s="150" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="K3" s="60" t="str">
         <v>Samaritano Higi</v>
       </c>
       <c r="M3" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N3" s="151" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="P3" s="159" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="R3" s="59" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="T3" s="84" t="s">
         <v>64</v>
       </c>
       <c r="V3" s="171" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="X3" s="148" t="s">
         <v>401</v>
@@ -66466,10 +66507,10 @@
         <v>193</v>
       </c>
       <c r="AB3" s="167" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="AD3" s="159" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="AF3" s="165" t="s">
         <v>78</v>
@@ -66495,7 +66536,7 @@
         <v>Forms Total Care</v>
       </c>
       <c r="H4" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="I4" s="150" t="s">
         <v>435</v>
@@ -66504,25 +66545,25 @@
         <v>COI -RJ</v>
       </c>
       <c r="M4" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N4" s="151" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="P4" s="159" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="R4" s="59" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="T4" s="84" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="V4" s="171" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="X4" s="167" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="Z4" s="59" t="s">
         <v>119</v>
@@ -66535,46 +66576,46 @@
       </c>
       <c r="AH4" s="160"/>
       <c r="AJ4" s="160" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="AL4" s="159" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="AN4" s="175"/>
     </row>
     <row r="5" spans="2:40">
       <c r="D5" s="73" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="F5" s="68" t="str">
         <v>GSC</v>
       </c>
       <c r="H5" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="I5" s="150" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="K5" s="60" t="str">
         <v>Interno - Amil Geral</v>
       </c>
       <c r="M5" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N5" s="151" t="s">
         <v>344</v>
       </c>
       <c r="P5" s="160" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="R5" s="59" t="s">
+        <v>555</v>
+      </c>
+      <c r="T5" s="86" t="s">
         <v>552</v>
       </c>
-      <c r="T5" s="86" t="s">
-        <v>549</v>
-      </c>
       <c r="V5" s="171" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="Z5" s="59"/>
       <c r="AD5" s="159" t="s">
@@ -66589,31 +66630,31 @@
     </row>
     <row r="6" spans="2:40">
       <c r="D6" s="73" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="F6" s="68" t="str">
         <v>Triggers</v>
       </c>
       <c r="H6" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="I6" s="150" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="K6" s="60" t="str">
         <v>Externo - Geral</v>
       </c>
       <c r="M6" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N6" s="151" t="s">
         <v>161</v>
       </c>
       <c r="R6" s="59" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="V6" s="171" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="Z6" s="225"/>
       <c r="AD6" s="160" t="s">
@@ -66630,25 +66671,25 @@
         <v xml:space="preserve">Viva Bem </v>
       </c>
       <c r="H7" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="I7" s="150" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="K7" s="60" t="str">
         <v>Não Informou</v>
       </c>
       <c r="M7" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N7" s="151" t="s">
         <v>143</v>
       </c>
       <c r="R7" s="59" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="V7" s="171" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="AD7" s="83"/>
       <c r="AF7" s="83"/>
@@ -66662,25 +66703,25 @@
         <v>Saúde Ocupacional</v>
       </c>
       <c r="H8" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="I8" s="150" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="K8" s="60" t="str">
         <v>CMDP - Centro Médico Dom Pedro</v>
       </c>
       <c r="M8" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N8" s="151" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="R8" s="59" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="V8" s="171" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="AD8" s="83"/>
       <c r="AF8" s="83"/>
@@ -66694,16 +66735,16 @@
         <v>Optin</v>
       </c>
       <c r="H9" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I9" s="152" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="K9" s="60" t="str">
         <v>Outros</v>
       </c>
       <c r="M9" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N9" s="151" t="s">
         <v>144</v>
@@ -66712,7 +66753,7 @@
         <v>67</v>
       </c>
       <c r="V9" s="171" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="Z9" s="1" t="s">
         <v>46</v>
@@ -66732,25 +66773,25 @@
         <v>Captado Total Care</v>
       </c>
       <c r="H10" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I10" s="153" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="K10" s="60" t="str">
         <v>Amil - Hospital Ipiranga Arujá - Ambulatório </v>
       </c>
       <c r="M10" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N10" s="151" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="R10" s="59" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="V10" s="171" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="Z10" s="1" t="s">
         <v>46</v>
@@ -66766,25 +66807,25 @@
     <row r="11" spans="2:40">
       <c r="F11" s="68"/>
       <c r="H11" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I11" s="153" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="K11" s="60" t="str">
         <v>Amil - Hospital Ipiranga Mogi - Ambulatório </v>
       </c>
       <c r="M11" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N11" s="151" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="R11" s="59" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="V11" s="171" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="Z11" s="1" t="s">
         <v>58</v>
@@ -66801,25 +66842,25 @@
     <row r="12" spans="2:40">
       <c r="F12" s="68"/>
       <c r="H12" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I12" s="153" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="K12" s="60" t="str">
         <v>Amil - Hospital Metropolitano - Centro Médico </v>
       </c>
       <c r="M12" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N12" s="151" t="s">
         <v>82</v>
       </c>
       <c r="R12" s="59" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="V12" s="171" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="Z12" s="1" t="s">
         <v>193</v>
@@ -66836,25 +66877,25 @@
     <row r="13" spans="2:40">
       <c r="F13" s="68"/>
       <c r="H13" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I13" s="153" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="K13" s="60" t="str">
         <v>Amil - Hospital Paulistano - Ambulatório </v>
       </c>
       <c r="M13" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N13" s="151" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="R13" s="59" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="V13" s="171" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="Z13" s="1" t="s">
         <v>119</v>
@@ -66871,28 +66912,28 @@
     <row r="14" spans="2:40">
       <c r="F14" s="68"/>
       <c r="H14" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I14" s="58" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="K14" s="60" t="str">
         <v>Amil - Ud Cubatão Sp - Hospital Da Luz </v>
       </c>
       <c r="M14" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N14" s="151" t="s">
         <v>327</v>
       </c>
       <c r="R14" s="59" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="V14" s="171" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AA14" s="1" t="s">
         <v>58</v>
@@ -66906,28 +66947,28 @@
     <row r="15" spans="2:40">
       <c r="F15" s="68"/>
       <c r="H15" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I15" s="58" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="K15" s="60" t="str">
         <v>Amil - Unidade Avançada Carlos Chagas </v>
       </c>
       <c r="M15" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N15" s="151" t="s">
         <v>153</v>
       </c>
       <c r="R15" s="59" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="V15" s="171" t="s">
         <v>118</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AA15" s="1" t="s">
         <v>193</v>
@@ -66941,28 +66982,28 @@
     <row r="16" spans="2:40">
       <c r="F16" s="68"/>
       <c r="H16" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I16" s="58" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="K16" s="60" t="str">
         <v>Amil - Unidade Avançada Luz Butantã </v>
       </c>
       <c r="M16" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N16" s="151" t="s">
         <v>73</v>
       </c>
       <c r="R16" s="59" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="V16" s="171" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AA16" s="1" t="s">
         <v>119</v>
@@ -66976,25 +67017,25 @@
     <row r="17" spans="6:38">
       <c r="F17" s="68"/>
       <c r="H17" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I17" s="58" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="K17" s="60" t="str">
         <v>Amil - Unidade Avançada Luz Joao Dias </v>
       </c>
       <c r="M17" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N17" s="151" t="s">
         <v>63</v>
       </c>
       <c r="R17" s="59" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="V17" s="171" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AD17" s="83"/>
       <c r="AF17" s="83"/>
@@ -67005,22 +67046,22 @@
     <row r="18" spans="6:38">
       <c r="F18" s="68"/>
       <c r="H18" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I18" s="58" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="K18" s="60" t="str">
         <v>Amil - Unidade Avançada Vitoria </v>
       </c>
       <c r="M18" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N18" s="151" t="s">
         <v>62</v>
       </c>
       <c r="R18" s="59" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="V18" s="171" t="s">
         <v>172</v>
@@ -67034,25 +67075,25 @@
     <row r="19" spans="6:38">
       <c r="F19" s="68"/>
       <c r="H19" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I19" s="58" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="K19" s="60" t="str">
         <v>Amil Espaço Saúde - Ana Rosa </v>
       </c>
       <c r="M19" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N19" s="151" t="s">
         <v>160</v>
       </c>
       <c r="R19" s="59" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="V19" s="171" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AD19" s="83"/>
       <c r="AF19" s="83"/>
@@ -67063,25 +67104,25 @@
     <row r="20" spans="6:38">
       <c r="F20" s="68"/>
       <c r="H20" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I20" s="58" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="K20" s="60" t="str">
         <v>Amil Espaço Saúde - Botafogo </v>
       </c>
       <c r="M20" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N20" s="151" t="s">
         <v>352</v>
       </c>
       <c r="R20" s="59" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="V20" s="171" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="Z20" s="1" t="str">
         <f>+Análise!$C$4</f>
@@ -67092,7 +67133,7 @@
         <v>Ativo</v>
       </c>
       <c r="AB20" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="AD20" s="83"/>
       <c r="AF20" s="83"/>
@@ -67103,31 +67144,31 @@
     <row r="21" spans="6:38">
       <c r="F21" s="68"/>
       <c r="H21" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I21" s="58" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="K21" s="60" t="str">
         <v>Amil Espaço Saúde - Campo Grande </v>
       </c>
       <c r="M21" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N21" s="151" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="R21" s="59" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="V21" s="171" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AA21" s="1" t="str">
         <v>Inativo</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="AD21" s="83"/>
       <c r="AF21" s="83"/>
@@ -67138,31 +67179,31 @@
     <row r="22" spans="6:38">
       <c r="F22" s="68"/>
       <c r="H22" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I22" s="58" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="K22" s="60" t="str">
         <v>Amil Espaço Saúde - Caxias </v>
       </c>
       <c r="M22" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N22" s="151" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="R22" s="59" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="V22" s="171" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="AA22" s="1" t="str">
         <v>Fora da Linha</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="AD22" s="83"/>
       <c r="AF22" s="83"/>
@@ -67173,28 +67214,28 @@
     <row r="23" spans="6:38">
       <c r="F23" s="68"/>
       <c r="H23" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I23" s="58" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="K23" s="60" t="str">
         <v>Amil Espaço Saúde - Guarulhos </v>
       </c>
       <c r="M23" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N23" s="151" t="s">
         <v>131</v>
       </c>
       <c r="R23" s="59" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="V23" s="171" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="AD23" s="83"/>
       <c r="AF23" s="83"/>
@@ -67205,22 +67246,22 @@
     <row r="24" spans="6:38" ht="15" thickBot="1">
       <c r="F24" s="68"/>
       <c r="H24" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I24" s="58" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="K24" s="60" t="str">
         <v>Amil Espaço Saúde - Niterói </v>
       </c>
       <c r="M24" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N24" s="151" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="R24" s="61" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="V24" s="171" t="s">
         <v>400</v>
@@ -67234,22 +67275,22 @@
     <row r="25" spans="6:38">
       <c r="F25" s="68"/>
       <c r="H25" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I25" s="58" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="K25" s="60" t="str">
         <v>Amil Espaço Saúde - Nova Iguaçu </v>
       </c>
       <c r="M25" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N25" s="151" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="V25" s="171" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AD25" s="83"/>
       <c r="AF25" s="83"/>
@@ -67260,22 +67301,22 @@
     <row r="26" spans="6:38" ht="15" thickBot="1">
       <c r="F26" s="68"/>
       <c r="H26" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I26" s="58" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="K26" s="60" t="str">
         <v>Amil Espaço Saúde - Osasco </v>
       </c>
       <c r="M26" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N26" s="151" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="V26" s="172" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AD26" s="83"/>
       <c r="AF26" s="83"/>
@@ -67286,16 +67327,16 @@
     <row r="27" spans="6:38">
       <c r="F27" s="68"/>
       <c r="H27" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I27" s="58" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="K27" s="60" t="str">
         <v>Amil Espaço Saúde - Santana </v>
       </c>
       <c r="M27" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N27" s="151" t="s">
         <v>302</v>
@@ -67312,16 +67353,16 @@
     <row r="28" spans="6:38">
       <c r="F28" s="68"/>
       <c r="H28" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I28" s="58" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="K28" s="60" t="str">
         <v>Amil Espaço Saúde - Tijuca </v>
       </c>
       <c r="M28" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N28" s="151" t="s">
         <v>104</v>
@@ -67333,19 +67374,19 @@
     <row r="29" spans="6:38">
       <c r="F29" s="68"/>
       <c r="H29" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I29" s="58" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="K29" s="60" t="str">
         <v>Amil Telemedicina </v>
       </c>
       <c r="M29" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N29" s="151" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="Z29" s="1" t="s">
         <v>193</v>
@@ -67354,19 +67395,19 @@
     <row r="30" spans="6:38">
       <c r="F30" s="68"/>
       <c r="H30" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I30" s="58" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="K30" s="60" t="str">
         <v>Centro Médico Jardim </v>
       </c>
       <c r="M30" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N30" s="151" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="Z30" s="1" t="s">
         <v>119</v>
@@ -67375,208 +67416,208 @@
     <row r="31" spans="6:38">
       <c r="F31" s="68"/>
       <c r="H31" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I31" s="58" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="K31" s="60" t="str">
         <v>Centro Médico Joao Azevedo - Sbc  II</v>
       </c>
       <c r="M31" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N31" s="151" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="32" spans="6:38">
       <c r="F32" s="68"/>
       <c r="H32" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I32" s="58" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="K32" s="60" t="str">
         <v>Centro Médico João Azevedo - Sbc I  </v>
       </c>
       <c r="M32" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N32" s="151" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
     </row>
     <row r="33" spans="6:14">
       <c r="F33" s="68"/>
       <c r="H33" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I33" s="58" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="K33" s="60" t="str">
         <v>Centro Médico Luiz Ferreira - Sbc </v>
       </c>
       <c r="M33" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N33" s="151" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="34" spans="6:14">
       <c r="F34" s="68"/>
       <c r="H34" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I34" s="58" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="K34" s="60" t="str">
         <v>Centro Médico - Samaritano Higienópolis </v>
       </c>
       <c r="M34" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N34" s="151" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
     </row>
     <row r="35" spans="6:14">
       <c r="F35" s="68"/>
       <c r="H35" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I35" s="58" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="K35" s="60" t="str">
         <v>Centro Médico Hospital São Lucas </v>
       </c>
       <c r="M35" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N35" s="151" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
     </row>
     <row r="36" spans="6:14">
       <c r="F36" s="68"/>
       <c r="H36" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I36" s="58" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="K36" s="60" t="str">
         <v>Hospital Alvorada Ambulatório Arapanés </v>
       </c>
       <c r="M36" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N36" s="151" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="37" spans="6:14">
       <c r="F37" s="68"/>
       <c r="H37" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I37" s="58" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="K37" s="60" t="str">
         <v>Hospital Alvorada Moema </v>
       </c>
       <c r="M37" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N37" s="151" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
     </row>
     <row r="38" spans="6:14">
       <c r="F38" s="68"/>
       <c r="H38" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I38" s="58" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="K38" s="60" t="str">
         <v>Hospital Américas - Ambulatório </v>
       </c>
       <c r="M38" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N38" s="151" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
     </row>
     <row r="39" spans="6:14">
       <c r="F39" s="68"/>
       <c r="H39" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I39" s="58" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="K39" s="60" t="str">
         <v>Hospital Samaritano Paulista - Ambulatório </v>
       </c>
       <c r="M39" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N39" s="151" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="40" spans="6:14">
       <c r="F40" s="68"/>
       <c r="H40" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I40" s="58" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="K40" s="60" t="str">
         <v>Amil Espaço Saúde - Tatuapé</v>
       </c>
       <c r="M40" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N40" s="58" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="41" spans="6:14">
       <c r="F41" s="68"/>
       <c r="H41" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I41" s="58" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="K41" s="60" t="str">
         <v>Amil Espaço Saúde - Santo Amaro</v>
       </c>
       <c r="M41" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N41" s="58" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
     <row r="42" spans="6:14">
       <c r="F42" s="68"/>
       <c r="H42" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I42" s="58" t="s">
         <v>440</v>
@@ -67585,112 +67626,112 @@
         <v>Amil Espaço Saúde - Guarulhos</v>
       </c>
       <c r="M42" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N42" s="58" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
     </row>
     <row r="43" spans="6:14">
       <c r="F43" s="68"/>
       <c r="H43" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I43" s="58" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="K43" s="60" t="str">
         <v xml:space="preserve">Amil Espaço Saúde - Santa Helena </v>
       </c>
       <c r="M43" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N43" s="58" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
     </row>
     <row r="44" spans="6:14">
       <c r="F44" s="68"/>
       <c r="H44" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I44" s="58" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="K44" s="60" t="str">
         <v>Hospital Samaritano - Não Especificado</v>
       </c>
       <c r="M44" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N44" s="58" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
     </row>
     <row r="45" spans="6:14">
       <c r="F45" s="68"/>
       <c r="H45" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I45" s="58" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="K45" s="60" t="str">
         <v>SUS</v>
       </c>
       <c r="M45" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N45" s="58" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
     </row>
     <row r="46" spans="6:14">
       <c r="F46" s="68"/>
       <c r="H46" s="79" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="I46" s="150" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="K46" s="60"/>
       <c r="M46" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N46" s="58" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
     </row>
     <row r="47" spans="6:14">
       <c r="F47" s="68"/>
       <c r="H47" s="229" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I47" s="230" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="K47" s="60"/>
       <c r="M47" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N47" s="58" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
     </row>
     <row r="48" spans="6:14">
       <c r="F48" s="68"/>
       <c r="H48" s="231" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="I48" s="232" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="K48" s="60"/>
       <c r="M48" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N48" s="58" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="49" spans="6:14">
@@ -67698,10 +67739,10 @@
       <c r="I49" s="62"/>
       <c r="K49" s="60"/>
       <c r="M49" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N49" s="58" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
     </row>
     <row r="50" spans="6:14">
@@ -67709,10 +67750,10 @@
       <c r="I50" s="62"/>
       <c r="K50" s="60"/>
       <c r="M50" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N50" s="58" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="51" spans="6:14">
@@ -67720,10 +67761,10 @@
       <c r="I51" s="62"/>
       <c r="K51" s="60"/>
       <c r="M51" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N51" s="58" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
     </row>
     <row r="52" spans="6:14">
@@ -67731,10 +67772,10 @@
       <c r="I52" s="62"/>
       <c r="K52" s="60"/>
       <c r="M52" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N52" s="58" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
     </row>
     <row r="53" spans="6:14">
@@ -67742,10 +67783,10 @@
       <c r="I53" s="62"/>
       <c r="K53" s="60"/>
       <c r="M53" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N53" s="58" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
     </row>
     <row r="54" spans="6:14" ht="15" thickBot="1">
@@ -67756,23 +67797,23 @@
       <c r="K54" s="63"/>
       <c r="L54" s="64"/>
       <c r="M54" s="38" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N54" s="58" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="55" spans="6:14" ht="15" thickBot="1">
       <c r="M55" s="156" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N55" s="157" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
     </row>
     <row r="56" spans="6:14">
       <c r="M56" s="200" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N56" s="201" t="s">
         <v>126</v>
@@ -67780,7 +67821,7 @@
     </row>
     <row r="57" spans="6:14">
       <c r="M57" s="200" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N57" s="201" t="s">
         <v>228</v>
@@ -67788,34 +67829,34 @@
     </row>
     <row r="58" spans="6:14">
       <c r="M58" s="200" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N58" s="201" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
     </row>
     <row r="59" spans="6:14">
       <c r="M59" s="200" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N59" s="202" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
     </row>
     <row r="60" spans="6:14">
       <c r="M60" s="200" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N60" s="203" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
     </row>
     <row r="61" spans="6:14">
       <c r="M61" s="200" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="N61" s="203" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
     </row>
     <row r="170" ht="15.75" customHeight="1"/>
@@ -67952,10 +67993,10 @@
         <v>29</v>
       </c>
       <c r="AE1" s="9" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="AF1" s="15" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="AG1" s="16" t="s">
         <v>35</v>
@@ -67967,10 +68008,10 @@
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
@@ -68004,7 +68045,7 @@
       </c>
       <c r="AA2" s="20"/>
       <c r="AB2" s="3" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="AC2" s="3"/>
       <c r="AD2" s="3" t="s">
@@ -68012,7 +68053,7 @@
       </c>
       <c r="AE2" s="3"/>
       <c r="AF2" s="3" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="AG2" s="17" t="s">
         <v>65</v>
@@ -68042,7 +68083,7 @@
       <c r="O3" s="17"/>
       <c r="P3" s="3"/>
       <c r="Q3" s="19" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="R3" s="3"/>
       <c r="S3" s="3"/>
@@ -68057,7 +68098,7 @@
       <c r="X3" s="3"/>
       <c r="Y3" s="3"/>
       <c r="Z3" s="3" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="AA3" s="3"/>
       <c r="AB3" s="3" t="s">
@@ -68069,20 +68110,20 @@
       </c>
       <c r="AE3" s="3"/>
       <c r="AF3" s="3" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="AG3" s="17" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
     </row>
     <row r="4" spans="1:33">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
@@ -68097,12 +68138,12 @@
       <c r="O4" s="17"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="19" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="U4" s="3"/>
       <c r="V4" s="3"/>
@@ -68122,7 +68163,7 @@
       </c>
       <c r="AE4" s="3"/>
       <c r="AF4" s="3" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="AG4" s="17" t="s">
         <v>47</v>
@@ -68132,97 +68173,97 @@
       <c r="M5" s="1"/>
       <c r="O5" s="1"/>
       <c r="Q5" s="22" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AB5" s="3" t="s">
         <v>60</v>
       </c>
       <c r="AF5" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="6" spans="1:33">
       <c r="M6" s="1"/>
       <c r="O6" s="1"/>
       <c r="Q6" s="23" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AF6" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
     </row>
     <row r="7" spans="1:33">
       <c r="M7" s="1"/>
       <c r="O7" s="1"/>
       <c r="Q7" s="23" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="AF7" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
     </row>
     <row r="8" spans="1:33">
       <c r="M8" s="1"/>
       <c r="O8" s="1"/>
       <c r="Q8" s="23" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="AF8" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
     </row>
     <row r="9" spans="1:33">
       <c r="M9" s="1"/>
       <c r="O9" s="1"/>
       <c r="Q9" s="23" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="AF9" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="10" spans="1:33">
       <c r="M10" s="1"/>
       <c r="O10" s="1"/>
       <c r="Q10" s="23" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AF10" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="AG10" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
     </row>
     <row r="11" spans="1:33">
       <c r="M11" s="1"/>
       <c r="O11" s="1"/>
       <c r="Q11" s="23" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AF11" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
     </row>
     <row r="12" spans="1:33">
       <c r="M12" s="1"/>
       <c r="O12" s="1"/>
       <c r="Q12" s="23" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="13" spans="1:33">
       <c r="M13" s="1"/>
       <c r="O13" s="1"/>
       <c r="Q13" s="23" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="14" spans="1:33">
       <c r="M14" s="1"/>
       <c r="O14" s="1"/>
       <c r="Q14" s="23" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="15" spans="1:33">
@@ -68236,17 +68277,17 @@
       <c r="M16" s="1"/>
       <c r="O16" s="1"/>
       <c r="Q16" s="23" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="17" spans="13:33">
       <c r="M17" s="1"/>
       <c r="O17" s="1"/>
       <c r="Q17" s="23" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AF17" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="18" spans="13:33" ht="43.15">
@@ -68256,20 +68297,20 @@
         <v>172</v>
       </c>
       <c r="AF18" s="24" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="AG18" s="24" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
     </row>
     <row r="19" spans="13:33">
       <c r="M19" s="1"/>
       <c r="O19" s="1"/>
       <c r="Q19" s="23" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="AF19" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="AG19" t="s">
         <v>66</v>
@@ -68279,10 +68320,10 @@
       <c r="M20" s="1"/>
       <c r="O20" s="1"/>
       <c r="Q20" s="23" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="AF20" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="AG20" t="s">
         <v>47</v>
@@ -68292,24 +68333,24 @@
       <c r="M21" s="1"/>
       <c r="O21" s="1"/>
       <c r="Q21" s="23" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AG21" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
     </row>
     <row r="22" spans="13:33">
       <c r="M22" s="1"/>
       <c r="O22" s="1"/>
       <c r="Q22" s="23" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="23" spans="13:33">
       <c r="M23" s="1"/>
       <c r="O23" s="1"/>
       <c r="Q23" s="23" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="24" spans="13:33">
@@ -68323,14 +68364,14 @@
       <c r="M25" s="1"/>
       <c r="O25" s="1"/>
       <c r="Q25" s="23" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="26" spans="13:33">
       <c r="M26" s="1"/>
       <c r="O26" s="1"/>
       <c r="Q26" s="23" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="27" spans="13:33">
